--- a/ScoresPossibles.xlsx
+++ b/ScoresPossibles.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,13 +37,17 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +57,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -87,23 +96,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -474,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -491,751 +507,785 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>En rouge : total impossible sans une boule dans le 15</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>♠ Pique</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>♣ Trèfle</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>♦ Carreau</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>♥ Cœur</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>✦ Tout atout</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>-10</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="4" t="n">
         <v>-10</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>-10</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>-10</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>-20</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>-12</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>-10</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>-8</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>-4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>-2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="4" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="4" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="4" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="4" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="4" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="4" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="4" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="4" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="4" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="4" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="4" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="C27" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="5" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="4" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="5" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="4" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="5" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="4" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="5" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="4" t="n">
         <v>52</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="C35" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="5" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="n">
+      <c r="B36" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C36" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="4" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="5" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="3" t="n">
+      <c r="B38" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C38" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="5" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="3" t="n">
+      <c r="B39" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="C39" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="5" t="n">
         <v>66</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="3" t="n">
+      <c r="B40" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="C40" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="5" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="3" t="n">
+      <c r="B41" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C41" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="4" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C42" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="4" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="3" t="n">
+      <c r="B43" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="C43" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="5" t="n">
         <v>39</v>
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="3" t="n">
+      <c r="C44" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="4" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="3" t="n">
+      <c r="C45" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="5" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="46">
-      <c r="C46" s="3" t="n">
+      <c r="C46" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="5" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="47">
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="4" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="48">
-      <c r="D48" s="3" t="n">
+      <c r="D48" s="4" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="49">
-      <c r="D49" s="3" t="n">
+      <c r="D49" s="4" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="50">
-      <c r="D50" s="3" t="n">
+      <c r="D50" s="5" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>33 totaux</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>40 totaux</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>43 totaux</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>47 totaux</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>37 totaux</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>dont 8 en rouge</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>dont 9 en rouge</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>dont 9 en rouge</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>dont 8 en rouge</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>dont 9 en rouge</t>
         </is>
       </c>
     </row>
@@ -1263,1499 +1313,1506 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Chaque total possible est marqué ✔ (case vide = total impossible)</t>
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>✔ en rouge : total impossible sans une boule dans le 15</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>♠ Pique</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>♣ Trèfle</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>♦ Carreau</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>♥ Cœur</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>✦ Tout atout</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="9" t="n">
         <v>-20</v>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="9" t="n">
         <v>-12</v>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="9" t="n">
         <v>-10</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="9" t="n">
         <v>-8</v>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="9" t="n">
         <v>-6</v>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n"/>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="n"/>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="n"/>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="n"/>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="n"/>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="n"/>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="n"/>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n"/>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="n">
+      <c r="A31" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="n"/>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="n">
+      <c r="A36" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="n"/>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="n">
+      <c r="A38" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="n"/>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="n">
+      <c r="A39" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="n">
+      <c r="A40" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="n"/>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="n">
+      <c r="A41" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="n">
+      <c r="A42" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="n"/>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="n">
+      <c r="A43" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B43" s="3" t="n"/>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="n">
+      <c r="A44" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="n"/>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="n">
+      <c r="A45" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="n">
+      <c r="A46" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n"/>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="n">
+      <c r="A47" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="n"/>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="n">
+      <c r="A48" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="n"/>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="n">
+      <c r="A49" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="B49" s="3" t="n"/>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="n">
+      <c r="A50" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="B50" s="3" t="n"/>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n"/>
-      <c r="F50" s="3" t="n"/>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="n">
+      <c r="A51" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n"/>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="n">
+      <c r="A52" s="9" t="n">
         <v>39</v>
       </c>
-      <c r="B52" s="3" t="n"/>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="n"/>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="n"/>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="n">
+      <c r="A53" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="B53" s="3" t="n"/>
-      <c r="C53" s="3" t="n"/>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="n">
+      <c r="A54" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="B54" s="3" t="n"/>
-      <c r="C54" s="3" t="n"/>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="n"/>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="n">
+      <c r="A55" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="B55" s="3" t="n"/>
-      <c r="C55" s="3" t="n"/>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n"/>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n"/>
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="n">
+      <c r="A56" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="B56" s="3" t="n"/>
-      <c r="C56" s="3" t="n"/>
-      <c r="D56" s="3" t="n"/>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="n"/>
+      <c r="B56" s="4" t="n"/>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="n">
+      <c r="A57" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="n"/>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="n">
+      <c r="A58" s="9" t="n">
         <v>46</v>
       </c>
-      <c r="B58" s="3" t="n"/>
-      <c r="C58" s="3" t="n"/>
-      <c r="D58" s="3" t="n"/>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="n">
+      <c r="A59" s="9" t="n">
         <v>47</v>
       </c>
-      <c r="B59" s="3" t="n"/>
-      <c r="C59" s="3" t="n"/>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="n"/>
-      <c r="F59" s="3" t="n"/>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="n"/>
+      <c r="F59" s="4" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="n">
+      <c r="A60" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
+      <c r="B60" s="4" t="n"/>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="n">
+      <c r="A61" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
-      <c r="E61" s="3" t="n"/>
-      <c r="F61" s="7" t="inlineStr">
+      <c r="B61" s="4" t="n"/>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="n">
+      <c r="A62" s="9" t="n">
         <v>52</v>
       </c>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="3" t="n"/>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="B62" s="4" t="n"/>
+      <c r="C62" s="4" t="n"/>
+      <c r="D62" s="4" t="n"/>
+      <c r="E62" s="4" t="n"/>
+      <c r="F62" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="n">
+      <c r="A63" s="9" t="n">
         <v>54</v>
       </c>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
-      <c r="E63" s="3" t="n"/>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="B63" s="4" t="n"/>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="n">
+      <c r="A64" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n"/>
-      <c r="D64" s="3" t="n"/>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="n"/>
+      <c r="B64" s="4" t="n"/>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="n">
+      <c r="A65" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="n"/>
-      <c r="E65" s="3" t="n"/>
-      <c r="F65" s="7" t="inlineStr">
+      <c r="B65" s="4" t="n"/>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="n">
+      <c r="A66" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="B66" s="3" t="n"/>
-      <c r="C66" s="3" t="n"/>
-      <c r="D66" s="3" t="n"/>
-      <c r="E66" s="3" t="n"/>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="n">
+      <c r="A67" s="9" t="n">
         <v>62</v>
       </c>
-      <c r="B67" s="3" t="n"/>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="n"/>
-      <c r="E67" s="3" t="n"/>
-      <c r="F67" s="7" t="inlineStr">
+      <c r="B67" s="4" t="n"/>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="5" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="n">
+      <c r="A68" s="9" t="n">
         <v>66</v>
       </c>
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="7" t="inlineStr">
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="n">
+      <c r="A69" s="9" t="n">
         <v>70</v>
       </c>
-      <c r="B69" s="3" t="n"/>
-      <c r="C69" s="3" t="n"/>
-      <c r="D69" s="3" t="n"/>
-      <c r="E69" s="3" t="n"/>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
@@ -2783,7 +2840,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>♠ Pique — valeur des trous : ♠ = 8 · ♣ = 6 · ♦ = 8 · ♥ = 10 · 15 = 15 · −5 = −5</t>
         </is>
@@ -2792,311 +2849,311 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>33 totaux possibles. 15 : Oui = exige le 15 · Peut-être = avec ou sans le 15 · — = sans le 15</t>
+          <t>33 totaux possibles. En rouge (Oui) = exige le 15 · Peut-être = avec ou sans le 15 · — = sans le 15</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Façons de l'obtenir (boules dans les trous ; les autres boules ratées = 0)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Calcul</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Avec le 15 ?</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="9" t="n">
         <v>-10</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>−5, −5</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>−5 − 5</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>−5</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>−5</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>♣, −5, −5</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>6 − 5 − 5</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>♦, −5, −5
 ♠, −5, −5</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>8 − 5 − 5
 8 − 5 − 5</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>3 boules ratées
 ♥, −5, −5</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>0
 10 − 5 − 5</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>♣, −5</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>6 − 5</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>♦, −5
 ♠, −5</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>8 − 5
 8 − 5</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>♥, −5
 15, −5, −5</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>10 − 5
 15 − 5 − 5</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>♣</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>♣, ♣, −5</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>6 + 6 − 5</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>♦
 ♠</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>8
 8</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>♦, ♣, −5
 ♣, ♠, −5</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>8 + 6 − 5
 6 + 8 − 5</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>♥
 15, −5</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>10
 15 − 5</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="18" ht="62" customHeight="1">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>♥, ♣, −5
 ♦, ♦, −5
@@ -3104,7 +3161,7 @@
 ♠, ♠, −5</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>10 + 6 − 5
 8 + 8 − 5
@@ -3112,103 +3169,103 @@
 8 + 8 − 5</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>♣, ♣</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>6 + 6</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>♥, ♦, −5
 ♥, ♠, −5</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>10 + 8 − 5
 10 + 8 − 5</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>♦, ♣
 ♣, ♠</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>8 + 6
 6 + 8</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>15
 ♥, ♥, −5</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>15
 10 + 10 − 5</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="23" ht="77" customHeight="1">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>♥, ♣
 ♦, ♦
@@ -3217,7 +3274,7 @@
 15, ♣, −5</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>10 + 6
 8 + 8
@@ -3226,17 +3283,17 @@
 15 + 6 − 5</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="24" ht="62" customHeight="1">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>♥, ♦
 ♥, ♠
@@ -3244,7 +3301,7 @@
 15, ♠, −5</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>10 + 8
 10 + 8
@@ -3252,17 +3309,17 @@
 15 + 8 − 5</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="25" ht="62" customHeight="1">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>♥, ♥
 15, ♥, −5
@@ -3270,7 +3327,7 @@
 ♣, ♣, ♠</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>10 + 10
 15 + 10 − 5
@@ -3278,37 +3335,37 @@
 6 + 6 + 8</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>15, ♣</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>15 + 6</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="27" ht="62" customHeight="1">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>♥, ♣, ♣
 ♦, ♦, ♣
@@ -3316,7 +3373,7 @@
 ♣, ♠, ♠</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>10 + 6 + 6
 8 + 8 + 6
@@ -3324,39 +3381,39 @@
 6 + 8 + 8</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>15, ♦
 15, ♠</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>15 + 8
 15 + 8</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="29" ht="62" customHeight="1">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>♥, ♦, ♣
 ♥, ♣, ♠
@@ -3364,7 +3421,7 @@
 ♦, ♠, ♠</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>10 + 8 + 6
 10 + 6 + 8
@@ -3372,37 +3429,37 @@
 8 + 8 + 8</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>15, ♥</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>15 + 10</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="31" ht="62" customHeight="1">
-      <c r="A31" s="6" t="n">
+      <c r="A31" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>♥, ♥, ♣
 ♥, ♦, ♦
@@ -3410,7 +3467,7 @@
 ♥, ♠, ♠</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>10 + 10 + 6
 10 + 8 + 8
@@ -3418,81 +3475,81 @@
 10 + 8 + 8</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>15, ♣, ♣</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>15 + 6 + 6</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>♥, ♥, ♦
 ♥, ♥, ♠</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>10 + 10 + 8
 10 + 10 + 8</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>15, ♦, ♣
 15, ♣, ♠</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>15 + 8 + 6
 15 + 6 + 8</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="35" ht="62" customHeight="1">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♣
 15, ♦, ♦
@@ -3500,7 +3557,7 @@
 15, ♠, ♠</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>15 + 10 + 6
 15 + 8 + 8
@@ -3508,49 +3565,49 @@
 15 + 8 + 8</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="6" t="n">
+      <c r="A36" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♦
 15, ♥, ♠</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>15 + 10 + 8
 15 + 10 + 8</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♥</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>15 + 10 + 10</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -3578,7 +3635,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>♣ Trèfle — valeur des trous : ♠ = 4 · ♣ = 12 · ♦ = 8 · ♥ = 10 · 15 = 15 · −5 = −5</t>
         </is>
@@ -3587,529 +3644,529 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>40 totaux possibles. 15 : Oui = exige le 15 · Peut-être = avec ou sans le 15 · — = sans le 15</t>
+          <t>40 totaux possibles. En rouge (Oui) = exige le 15 · Peut-être = avec ou sans le 15 · — = sans le 15</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Façons de l'obtenir (boules dans les trous ; les autres boules ratées = 0)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Calcul</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Avec le 15 ?</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="9" t="n">
         <v>-10</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>−5, −5</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>−5 − 5</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="9" t="n">
         <v>-6</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>♠, −5, −5</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>4 − 5 − 5</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>−5</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>−5</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>♦, −5, −5</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>8 − 5 − 5</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>♠, −5</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>4 − 5</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>3 boules ratées
 ♥, −5, −5</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>0
 10 − 5 − 5</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>♣, −5, −5</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>12 − 5 − 5</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>♦, −5
 ♠, ♠, −5</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>8 − 5
 4 + 4 − 5</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>♠</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>♥, −5
 15, −5, −5</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>10 − 5
 15 − 5 − 5</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>♣, −5
 ♦, ♠, −5</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>12 − 5
 8 + 4 − 5</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>♦
 ♠, ♠</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>8
 4 + 4</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>♥, ♠, −5</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>10 + 4 − 5</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>♥
 15, −5</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>10
 15 − 5</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>♦, ♦, −5
 ♣, ♠, −5</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>8 + 8 − 5
 12 + 4 − 5</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>♣
 ♦, ♠</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>12
 8 + 4</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>♥, ♦, −5</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>10 + 8 − 5</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>♥, ♠
 15, ♠, −5</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>10 + 4
 15 + 4 − 5</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="23" ht="47" customHeight="1">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>15
 ♥, ♥, −5
 ♦, ♣, −5</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>15
 10 + 10 − 5
 8 + 12 − 5</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="24" ht="47" customHeight="1">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>♦, ♦
 ♣, ♠
 ♦, ♠, ♠</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>8 + 8
 12 + 4
 8 + 4 + 4</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>♥, ♣, −5</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>10 + 12 − 5</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="26" ht="47" customHeight="1">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>♥, ♦
 15, ♦, −5
 ♥, ♠, ♠</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>10 + 8
 15 + 8 − 5
 10 + 4 + 4</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>15, ♠
 ♣, ♣, −5</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>15 + 4
 12 + 12 − 5</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="28" ht="77" customHeight="1">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>♥, ♥
 ♦, ♣
@@ -4118,7 +4175,7 @@
 ♣, ♠, ♠</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>10 + 10
 8 + 12
@@ -4127,351 +4184,351 @@
 12 + 4 + 4</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="29" ht="47" customHeight="1">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>♥, ♣
 15, ♣, −5
 ♥, ♦, ♠</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>10 + 12
 15 + 12 − 5
 10 + 8 + 4</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>15, ♦
 15, ♠, ♠</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>15 + 8
 15 + 4 + 4</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="31" ht="47" customHeight="1">
-      <c r="A31" s="6" t="n">
+      <c r="A31" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>♣, ♣
 ♥, ♥, ♠
 ♦, ♣, ♠</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>12 + 12
 10 + 10 + 4
 8 + 12 + 4</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>15, ♥</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>15 + 10</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>♥, ♦, ♦
 ♥, ♣, ♠</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>10 + 8 + 8
 10 + 12 + 4</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>15, ♣
 15, ♦, ♠</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>15 + 12
 15 + 8 + 4</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="35" ht="47" customHeight="1">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>♥, ♥, ♦
 ♦, ♦, ♣
 ♣, ♣, ♠</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>10 + 10 + 8
 8 + 8 + 12
 12 + 12 + 4</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="6" t="n">
+      <c r="A36" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♠</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>15 + 10 + 4</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>♥, ♦, ♣</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>10 + 8 + 12</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="6" t="n">
+      <c r="A38" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>15, ♦, ♦
 15, ♣, ♠</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>15 + 8 + 8
 15 + 12 + 4</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="6" t="n">
+      <c r="A39" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>♥, ♥, ♣
 ♦, ♣, ♣</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>10 + 10 + 12
 8 + 12 + 12</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="6" t="n">
+      <c r="A40" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♦</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>15 + 10 + 8</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="6" t="n">
+      <c r="A41" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>♥, ♣, ♣</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>10 + 12 + 12</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="6" t="n">
+      <c r="A42" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♥
 15, ♦, ♣</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>15 + 10 + 10
 15 + 8 + 12</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="6" t="n">
+      <c r="A43" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♣</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>15 + 10 + 12</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="6" t="n">
+      <c r="A44" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>15, ♣, ♣</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>15 + 12 + 12</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -4499,7 +4556,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>♦ Carreau — valeur des trous : ♠ = 4 · ♣ = 6 · ♦ = 16 · ♥ = 10 · 15 = 15 · −5 = −5</t>
         </is>
@@ -4508,439 +4565,439 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>43 totaux possibles. 15 : Oui = exige le 15 · Peut-être = avec ou sans le 15 · — = sans le 15</t>
+          <t>43 totaux possibles. En rouge (Oui) = exige le 15 · Peut-être = avec ou sans le 15 · — = sans le 15</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Façons de l'obtenir (boules dans les trous ; les autres boules ratées = 0)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Calcul</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Avec le 15 ?</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="9" t="n">
         <v>-10</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>−5, −5</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>−5 − 5</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="9" t="n">
         <v>-6</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>♠, −5, −5</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>4 − 5 − 5</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>−5</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>−5</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>♣, −5, −5</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>6 − 5 − 5</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>♠, −5</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>4 − 5</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>3 boules ratées
 ♥, −5, −5</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>0
 10 − 5 − 5</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>♣, −5</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>6 − 5</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>♠, ♠, −5</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>4 + 4 − 5</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>♠</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="14" ht="47" customHeight="1">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>♥, −5
 15, −5, −5
 ♣, ♠, −5</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>10 − 5
 15 − 5 − 5
 6 + 4 − 5</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>♣
 ♦, −5, −5</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>6
 16 − 5 − 5</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>♣, ♣, −5</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>6 + 6 − 5</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>♠, ♠</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>4 + 4</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>♥, ♠, −5</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>10 + 4 − 5</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="19" ht="47" customHeight="1">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>♥
 15, −5
 ♣, ♠</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>10
 15 − 5
 6 + 4</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>♦, −5
 ♥, ♣, −5</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>16 − 5
 10 + 6 − 5</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>♣, ♣</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>6 + 6</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="22" ht="47" customHeight="1">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>♥, ♠
 15, ♠, −5
 ♣, ♠, ♠</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>10 + 4
 15 + 4 − 5
 6 + 4 + 4</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="23" ht="47" customHeight="1">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>15
 ♥, ♥, −5
 ♦, ♠, −5</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>15
 10 + 10 − 5
 16 + 4 − 5</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="24" ht="62" customHeight="1">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>♦
 ♥, ♣
@@ -4948,7 +5005,7 @@
 ♣, ♣, ♠</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>16
 10 + 6
@@ -4956,77 +5013,77 @@
 6 + 6 + 4</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>♦, ♣, −5</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>16 + 6 − 5</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>♥, ♠, ♠</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>10 + 4 + 4</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>15, ♠</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>15 + 4</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="28" ht="62" customHeight="1">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>♥, ♥
 ♦, ♠
@@ -5034,7 +5091,7 @@
 ♥, ♣, ♠</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>10 + 10
 16 + 4
@@ -5042,125 +5099,125 @@
 10 + 6 + 4</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>15, ♣
 ♥, ♦, −5</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>15 + 6
 10 + 16 − 5</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>♦, ♣
 ♥, ♣, ♣</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>16 + 6
 10 + 6 + 6</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="6" t="n">
+      <c r="A31" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>15, ♠, ♠</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>15 + 4 + 4</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>♥, ♥, ♠
 ♦, ♠, ♠</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>10 + 10 + 4
 16 + 4 + 4</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>15, ♥
 15, ♣, ♠</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>15 + 10
 15 + 6 + 4</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="34" ht="62" customHeight="1">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>♥, ♦
 15, ♦, −5
@@ -5168,7 +5225,7 @@
 ♦, ♣, ♠</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>10 + 16
 15 + 16 − 5
@@ -5176,277 +5233,277 @@
 16 + 6 + 4</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>15, ♣, ♣
 ♦, ♦, −5</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>15 + 6 + 6
 16 + 16 − 5</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="6" t="n">
+      <c r="A36" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>♦, ♣, ♣</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>16 + 6 + 6</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♠</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>15 + 10 + 4</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="6" t="n">
+      <c r="A38" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>♥, ♦, ♠</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>10 + 16 + 4</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="6" t="n">
+      <c r="A39" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>15, ♦
 15, ♥, ♣</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>15 + 16
 15 + 10 + 6</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="6" t="n">
+      <c r="A40" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>♦, ♦
 ♥, ♦, ♣</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>16 + 16
 10 + 16 + 6</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="6" t="n">
+      <c r="A41" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♥
 15, ♦, ♠</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>15 + 10 + 10
 15 + 16 + 4</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="6" t="n">
+      <c r="A42" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>♥, ♥, ♦
 ♦, ♦, ♠</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>10 + 10 + 16
 16 + 16 + 4</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="6" t="n">
+      <c r="A43" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>15, ♦, ♣</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>15 + 16 + 6</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="6" t="n">
+      <c r="A44" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>♦, ♦, ♣</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>16 + 16 + 6</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="6" t="n">
+      <c r="A45" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♦</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>15 + 10 + 16</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="6" t="n">
+      <c r="A46" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>♥, ♦, ♦</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>10 + 16 + 16</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="6" t="n">
+      <c r="A47" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>15, ♦, ♦</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>15 + 16 + 16</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -5474,7 +5531,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>♥ Cœur — valeur des trous : ♠ = 4 · ♣ = 6 · ♦ = 8 · ♥ = 20 · 15 = 15 · −5 = −5</t>
         </is>
@@ -5483,457 +5540,457 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>47 totaux possibles. 15 : Oui = exige le 15 · Peut-être = avec ou sans le 15 · — = sans le 15</t>
+          <t>47 totaux possibles. En rouge (Oui) = exige le 15 · Peut-être = avec ou sans le 15 · — = sans le 15</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Façons de l'obtenir (boules dans les trous ; les autres boules ratées = 0)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Calcul</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Avec le 15 ?</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="9" t="n">
         <v>-10</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>−5, −5</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>−5 − 5</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="9" t="n">
         <v>-6</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>♠, −5, −5</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>4 − 5 − 5</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>−5</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>−5</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>♣, −5, −5</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>6 − 5 − 5</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>♦, −5, −5</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>8 − 5 − 5</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>♠, −5</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>4 − 5</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>3 boules ratées</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>♣, −5</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>6 − 5</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>♦, −5
 ♠, ♠, −5</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>8 − 5
 4 + 4 − 5</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>♠</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>15, −5, −5
 ♣, ♠, −5</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>15 − 5 − 5
 6 + 4 − 5</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>♣</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>♦, ♠, −5
 ♣, ♣, −5</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>8 + 4 − 5
 6 + 6 − 5</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>♦
 ♠, ♠</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>8
 4 + 4</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>♦, ♣, −5</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>8 + 6 − 5</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="20" ht="47" customHeight="1">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>15, −5
 ♣, ♠
 ♥, −5, −5</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>15 − 5
 6 + 4
 20 − 5 − 5</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>♦, ♦, −5</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>8 + 8 − 5</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>♦, ♠
 ♣, ♣</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>8 + 4
 6 + 6</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="23" ht="47" customHeight="1">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>♦, ♣
 15, ♠, −5
 ♣, ♠, ♠</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>8 + 6
 15 + 4 − 5
 6 + 4 + 4</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>15
 ♥, −5</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>15
 20 − 5</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="25" ht="62" customHeight="1">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>♦, ♦
 15, ♣, −5
@@ -5941,7 +5998,7 @@
 ♣, ♣, ♠</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>8 + 8
 15 + 6 − 5
@@ -5949,551 +6006,551 @@
 6 + 6 + 4</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>15, ♦, −5
 ♦, ♣, ♠</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>15 + 8 − 5
 8 + 6 + 4</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>15, ♠
 ♥, ♠, −5</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>15 + 4
 20 + 4 − 5</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="28" ht="47" customHeight="1">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>♥
 ♦, ♦, ♠
 ♦, ♣, ♣</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>20
 8 + 8 + 4
 8 + 6 + 6</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>15, ♣
 ♥, ♣, −5</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>15 + 6
 20 + 6 − 5</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>♦, ♦, ♣</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>8 + 8 + 6</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="31" ht="47" customHeight="1">
-      <c r="A31" s="6" t="n">
+      <c r="A31" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>15, ♦
 15, ♠, ♠
 ♥, ♦, −5</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>15 + 8
 15 + 4 + 4
 20 + 8 − 5</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>♥, ♠</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>20 + 4</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>15, ♣, ♠</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>15 + 6 + 4</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>♥, ♣</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>20 + 6</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>15, ♦, ♠
 15, ♣, ♣</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>15 + 8 + 4
 15 + 6 + 6</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="6" t="n">
+      <c r="A36" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>♥, ♦
 ♥, ♠, ♠</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>20 + 8
 20 + 4 + 4</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>15, ♦, ♣</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>15 + 8 + 6</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="6" t="n">
+      <c r="A38" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>15, ♥, −5
 ♥, ♣, ♠</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>15 + 20 − 5
 20 + 6 + 4</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="6" t="n">
+      <c r="A39" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>15, ♦, ♦</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>15 + 8 + 8</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="6" t="n">
+      <c r="A40" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>♥, ♦, ♠
 ♥, ♣, ♣</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>20 + 8 + 4
 20 + 6 + 6</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="6" t="n">
+      <c r="A41" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>♥, ♦, ♣</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>20 + 8 + 6</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="6" t="n">
+      <c r="A42" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>15, ♥
 ♥, ♥, −5</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>15 + 20
 20 + 20 − 5</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="6" t="n">
+      <c r="A43" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>♥, ♦, ♦</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>20 + 8 + 8</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="6" t="n">
+      <c r="A44" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♠</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>15 + 20 + 4</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="6" t="n">
+      <c r="A45" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>♥, ♥</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>20 + 20</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="6" t="n">
+      <c r="A46" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♣</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>15 + 20 + 6</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="6" t="n">
+      <c r="A47" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♦</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>15 + 20 + 8</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="6" t="n">
+      <c r="A48" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>♥, ♥, ♠</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>20 + 20 + 4</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="6" t="n">
+      <c r="A49" s="9" t="n">
         <v>46</v>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>♥, ♥, ♣</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>20 + 20 + 6</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="6" t="n">
+      <c r="A50" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>♥, ♥, ♦</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>20 + 20 + 8</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="6" t="n">
+      <c r="A51" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♥</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>15 + 20 + 20</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
@@ -6521,7 +6578,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>✦ Tout atout — valeur des trous : ♠ = 8 · ♣ = 12 · ♦ = 16 · ♥ = 20 · 15 = 30 · −5 = −10</t>
         </is>
@@ -6530,439 +6587,439 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>37 totaux possibles. 15 : Oui = exige le 15 · Peut-être = avec ou sans le 15 · — = sans le 15</t>
+          <t>37 totaux possibles. En rouge (Oui) = exige le 15 · Peut-être = avec ou sans le 15 · — = sans le 15</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Façons de l'obtenir (boules dans les trous ; les autres boules ratées = 0)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Calcul</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Avec le 15 ?</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="9" t="n">
         <v>-20</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>−5, −5</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>−10 − 10</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="9" t="n">
         <v>-12</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>♠, −5, −5</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>8 − 10 − 10</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="9" t="n">
         <v>-10</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>−5</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>−10</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="9" t="n">
         <v>-8</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>♣, −5, −5</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>12 − 10 − 10</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>♦, −5, −5</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>16 − 10 − 10</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>♠, −5</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>8 − 10</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>3 boules ratées
 ♥, −5, −5</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>0
 20 − 10 − 10</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>♣, −5</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>12 − 10</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>♦, −5
 ♠, ♠, −5</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>16 − 10
 8 + 8 − 10</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>♠</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="15" ht="47" customHeight="1">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>♥, −5
 15, −5, −5
 ♣, ♠, −5</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>20 − 10
 30 − 10 − 10
 12 + 8 − 10</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>♣</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>♦, ♠, −5
 ♣, ♣, −5</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>16 + 8 − 10
 12 + 12 − 10</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>♦
 ♠, ♠</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>16
 8 + 8</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>♥, ♠, −5
 ♦, ♣, −5</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>20 + 8 − 10
 16 + 12 − 10</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="20" ht="47" customHeight="1">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>♥
 15, −5
 ♣, ♠</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>20
 30 − 10
 12 + 8</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>♥, ♣, −5
 ♦, ♦, −5</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>20 + 12 − 10
 16 + 16 − 10</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>♦, ♠
 ♣, ♣</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>16 + 8
 12 + 12</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>♥, ♦, −5</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>20 + 16 − 10</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="24" ht="62" customHeight="1">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>♥, ♠
 ♦, ♣
@@ -6970,7 +7027,7 @@
 ♣, ♠, ♠</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>20 + 8
 16 + 12
@@ -6978,39 +7035,39 @@
 12 + 8 + 8</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>15
 ♥, ♥, −5</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>30
 20 + 20 − 10</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="26" ht="77" customHeight="1">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>♥, ♣
 ♦, ♦
@@ -7019,7 +7076,7 @@
 ♣, ♣, ♠</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>20 + 12
 16 + 16
@@ -7028,17 +7085,17 @@
 12 + 12 + 8</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="27" ht="62" customHeight="1">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>♥, ♦
 15, ♦, −5
@@ -7046,7 +7103,7 @@
 ♦, ♣, ♠</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>20 + 16
 30 + 16 − 10
@@ -7054,37 +7111,37 @@
 16 + 12 + 8</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>15, ♠</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>30 + 8</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="29" ht="77" customHeight="1">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>♥, ♥
 15, ♥, −5
@@ -7093,7 +7150,7 @@
 ♦, ♣, ♣</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>20 + 20
 30 + 20 − 10
@@ -7102,265 +7159,265 @@
 16 + 12 + 12</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Peut-être</t>
         </is>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>15, ♣</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>30 + 12</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="31" ht="47" customHeight="1">
-      <c r="A31" s="6" t="n">
+      <c r="A31" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>♥, ♦, ♠
 ♥, ♣, ♣
 ♦, ♦, ♣</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>20 + 16 + 8
 20 + 12 + 12
 16 + 16 + 12</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>15, ♦
 15, ♠, ♠</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>30 + 16
 30 + 8 + 8</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>♥, ♥, ♠
 ♥, ♦, ♣</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>20 + 20 + 8
 20 + 16 + 12</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>15, ♥
 15, ♣, ♠</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>30 + 20
 30 + 12 + 8</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="9" t="n">
         <v>52</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>♥, ♥, ♣
 ♥, ♦, ♦</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>20 + 20 + 12
 20 + 16 + 16</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="6" t="n">
+      <c r="A36" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>15, ♦, ♠
 15, ♣, ♣</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>30 + 16 + 8
 30 + 12 + 12</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>♥, ♥, ♦</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>20 + 20 + 16</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="6" t="n">
+      <c r="A38" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♠
 15, ♦, ♣</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>30 + 20 + 8
 30 + 16 + 12</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="6" t="n">
+      <c r="A39" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♣
 15, ♦, ♦</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>30 + 20 + 12
 30 + 16 + 16</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="6" t="n">
+      <c r="A40" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♦</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>30 + 20 + 16</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="6" t="n">
+      <c r="A41" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>15, ♥, ♥</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>30 + 20 + 20</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>

--- a/ScoresPossibles.xlsx
+++ b/ScoresPossibles.xlsx
@@ -2853,6 +2853,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Chaque ligne compte les 3 boules : 0, 1, 2 ou 3 boules peuvent rater (0 point chacune).</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2861,7 +2868,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Façons de l'obtenir (boules dans les trous ; les autres boules ratées = 0)</t>
+          <t>Façons de l'obtenir avec les 3 boules (ratée = boule dans aucun trou, 0 point)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2881,12 +2888,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>−5, −5</t>
+          <t>−5, −5, ratée</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>−5 − 5</t>
+          <t>−5 − 5 + 0</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -2901,12 +2908,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>−5</t>
+          <t>−5, ratée, ratée</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>−5</t>
+          <t>−5 + 0 + 0</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -2963,13 +2970,13 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>3 boules ratées
+          <t>ratée, ratée, ratée
 ♥, −5, −5</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>0
+          <t>0 + 0 + 0
 10 − 5 − 5</t>
         </is>
       </c>
@@ -2985,12 +2992,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>♣, −5</t>
+          <t>♣, −5, ratée</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>6 − 5</t>
+          <t>6 − 5 + 0</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -3005,14 +3012,14 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>♦, −5
-♠, −5</t>
+          <t>♦, −5, ratée
+♠, −5, ratée</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>8 − 5
-8 − 5</t>
+          <t>8 − 5 + 0
+8 − 5 + 0</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -3027,13 +3034,13 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>♥, −5
+          <t>♥, −5, ratée
 15, −5, −5</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>10 − 5
+          <t>10 − 5 + 0
 15 − 5 − 5</t>
         </is>
       </c>
@@ -3049,12 +3056,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>♣</t>
+          <t>♣, ratée, ratée</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6 + 0 + 0</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -3089,14 +3096,14 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>♦
-♠</t>
+          <t>♦, ratée, ratée
+♠, ratée, ratée</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>8
-8</t>
+          <t>8 + 0 + 0
+8 + 0 + 0</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -3133,14 +3140,14 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>♥
-15, −5</t>
+          <t>♥, ratée, ratée
+15, −5, ratée</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>10
-15 − 5</t>
+          <t>10 + 0 + 0
+15 − 5 + 0</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -3181,12 +3188,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>♣, ♣</t>
+          <t>♣, ♣, ratée</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>6 + 6</t>
+          <t>6 + 6 + 0</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -3223,14 +3230,14 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>♦, ♣
-♣, ♠</t>
+          <t>♦, ♣, ratée
+♣, ♠, ratée</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>8 + 6
-6 + 8</t>
+          <t>8 + 6 + 0
+6 + 8 + 0</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -3245,13 +3252,13 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>15
+          <t>15, ratée, ratée
 ♥, ♥, −5</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>15
+          <t>15 + 0 + 0
 10 + 10 − 5</t>
         </is>
       </c>
@@ -3267,19 +3274,19 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>♥, ♣
-♦, ♦
-♦, ♠
-♠, ♠
+          <t>♥, ♣, ratée
+♦, ♦, ratée
+♦, ♠, ratée
+♠, ♠, ratée
 15, ♣, −5</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>10 + 6
-8 + 8
-8 + 8
-8 + 8
+          <t>10 + 6 + 0
+8 + 8 + 0
+8 + 8 + 0
+8 + 8 + 0
 15 + 6 − 5</t>
         </is>
       </c>
@@ -3295,16 +3302,16 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>♥, ♦
-♥, ♠
+          <t>♥, ♦, ratée
+♥, ♠, ratée
 15, ♦, −5
 15, ♠, −5</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>10 + 8
-10 + 8
+          <t>10 + 8 + 0
+10 + 8 + 0
 15 + 8 − 5
 15 + 8 − 5</t>
         </is>
@@ -3321,7 +3328,7 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>♥, ♥
+          <t>♥, ♥, ratée
 15, ♥, −5
 ♦, ♣, ♣
 ♣, ♣, ♠</t>
@@ -3329,7 +3336,7 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>10 + 10
+          <t>10 + 10 + 0
 15 + 10 − 5
 8 + 6 + 6
 6 + 6 + 8</t>
@@ -3347,12 +3354,12 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>15, ♣</t>
+          <t>15, ♣, ratée</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>15 + 6</t>
+          <t>15 + 6 + 0</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -3393,14 +3400,14 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>15, ♦
-15, ♠</t>
+          <t>15, ♦, ratée
+15, ♠, ratée</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>15 + 8
-15 + 8</t>
+          <t>15 + 8 + 0
+15 + 8 + 0</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -3441,12 +3448,12 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>15, ♥</t>
+          <t>15, ♥, ratée</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>15 + 10</t>
+          <t>15 + 10 + 0</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -3648,6 +3655,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Chaque ligne compte les 3 boules : 0, 1, 2 ou 3 boules peuvent rater (0 point chacune).</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3656,7 +3670,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Façons de l'obtenir (boules dans les trous ; les autres boules ratées = 0)</t>
+          <t>Façons de l'obtenir avec les 3 boules (ratée = boule dans aucun trou, 0 point)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3676,12 +3690,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>−5, −5</t>
+          <t>−5, −5, ratée</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>−5 − 5</t>
+          <t>−5 − 5 + 0</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -3716,12 +3730,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>−5</t>
+          <t>−5, ratée, ratée</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>−5</t>
+          <t>−5 + 0 + 0</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -3756,12 +3770,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>♠, −5</t>
+          <t>♠, −5, ratée</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>4 − 5</t>
+          <t>4 − 5 + 0</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -3776,13 +3790,13 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>3 boules ratées
+          <t>ratée, ratée, ratée
 ♥, −5, −5</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>0
+          <t>0 + 0 + 0
 10 − 5 − 5</t>
         </is>
       </c>
@@ -3818,13 +3832,13 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>♦, −5
+          <t>♦, −5, ratée
 ♠, ♠, −5</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>8 − 5
+          <t>8 − 5 + 0
 4 + 4 − 5</t>
         </is>
       </c>
@@ -3840,12 +3854,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>♠</t>
+          <t>♠, ratée, ratée</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 + 0 + 0</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -3860,13 +3874,13 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>♥, −5
+          <t>♥, −5, ratée
 15, −5, −5</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>10 − 5
+          <t>10 − 5 + 0
 15 − 5 − 5</t>
         </is>
       </c>
@@ -3882,13 +3896,13 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>♣, −5
+          <t>♣, −5, ratée
 ♦, ♠, −5</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>12 − 5
+          <t>12 − 5 + 0
 8 + 4 − 5</t>
         </is>
       </c>
@@ -3904,14 +3918,14 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>♦
-♠, ♠</t>
+          <t>♦, ratée, ratée
+♠, ♠, ratée</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>8
-4 + 4</t>
+          <t>8 + 0 + 0
+4 + 4 + 0</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -3946,14 +3960,14 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>♥
-15, −5</t>
+          <t>♥, ratée, ratée
+15, −5, ratée</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>10
-15 − 5</t>
+          <t>10 + 0 + 0
+15 − 5 + 0</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -3990,14 +4004,14 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>♣
-♦, ♠</t>
+          <t>♣, ratée, ratée
+♦, ♠, ratée</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>12
-8 + 4</t>
+          <t>12 + 0 + 0
+8 + 4 + 0</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -4032,13 +4046,13 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>♥, ♠
+          <t>♥, ♠, ratée
 15, ♠, −5</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>10 + 4
+          <t>10 + 4 + 0
 15 + 4 − 5</t>
         </is>
       </c>
@@ -4054,14 +4068,14 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>15
+          <t>15, ratée, ratée
 ♥, ♥, −5
 ♦, ♣, −5</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>15
+          <t>15 + 0 + 0
 10 + 10 − 5
 8 + 12 − 5</t>
         </is>
@@ -4078,15 +4092,15 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>♦, ♦
-♣, ♠
+          <t>♦, ♦, ratée
+♣, ♠, ratée
 ♦, ♠, ♠</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>8 + 8
-12 + 4
+          <t>8 + 8 + 0
+12 + 4 + 0
 8 + 4 + 4</t>
         </is>
       </c>
@@ -4122,14 +4136,14 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>♥, ♦
+          <t>♥, ♦, ratée
 15, ♦, −5
 ♥, ♠, ♠</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>10 + 8
+          <t>10 + 8 + 0
 15 + 8 − 5
 10 + 4 + 4</t>
         </is>
@@ -4146,13 +4160,13 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>15, ♠
+          <t>15, ♠, ratée
 ♣, ♣, −5</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>15 + 4
+          <t>15 + 4 + 0
 12 + 12 − 5</t>
         </is>
       </c>
@@ -4168,8 +4182,8 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>♥, ♥
-♦, ♣
+          <t>♥, ♥, ratée
+♦, ♣, ratée
 15, ♥, −5
 ♦, ♦, ♠
 ♣, ♠, ♠</t>
@@ -4177,8 +4191,8 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>10 + 10
-8 + 12
+          <t>10 + 10 + 0
+8 + 12 + 0
 15 + 10 − 5
 8 + 8 + 4
 12 + 4 + 4</t>
@@ -4196,14 +4210,14 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>♥, ♣
+          <t>♥, ♣, ratée
 15, ♣, −5
 ♥, ♦, ♠</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>10 + 12
+          <t>10 + 12 + 0
 15 + 12 − 5
 10 + 8 + 4</t>
         </is>
@@ -4220,13 +4234,13 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>15, ♦
+          <t>15, ♦, ratée
 15, ♠, ♠</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>15 + 8
+          <t>15 + 8 + 0
 15 + 4 + 4</t>
         </is>
       </c>
@@ -4242,14 +4256,14 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>♣, ♣
+          <t>♣, ♣, ratée
 ♥, ♥, ♠
 ♦, ♣, ♠</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>12 + 12
+          <t>12 + 12 + 0
 10 + 10 + 4
 8 + 12 + 4</t>
         </is>
@@ -4266,12 +4280,12 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>15, ♥</t>
+          <t>15, ♥, ratée</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>15 + 10</t>
+          <t>15 + 10 + 0</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -4308,13 +4322,13 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>15, ♣
+          <t>15, ♣, ratée
 15, ♦, ♠</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>15 + 12
+          <t>15 + 12 + 0
 15 + 8 + 4</t>
         </is>
       </c>
@@ -4569,6 +4583,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Chaque ligne compte les 3 boules : 0, 1, 2 ou 3 boules peuvent rater (0 point chacune).</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4577,7 +4598,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Façons de l'obtenir (boules dans les trous ; les autres boules ratées = 0)</t>
+          <t>Façons de l'obtenir avec les 3 boules (ratée = boule dans aucun trou, 0 point)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -4597,12 +4618,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>−5, −5</t>
+          <t>−5, −5, ratée</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>−5 − 5</t>
+          <t>−5 − 5 + 0</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -4637,12 +4658,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>−5</t>
+          <t>−5, ratée, ratée</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>−5</t>
+          <t>−5 + 0 + 0</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -4677,12 +4698,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>♠, −5</t>
+          <t>♠, −5, ratée</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>4 − 5</t>
+          <t>4 − 5 + 0</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -4697,13 +4718,13 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>3 boules ratées
+          <t>ratée, ratée, ratée
 ♥, −5, −5</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>0
+          <t>0 + 0 + 0
 10 − 5 − 5</t>
         </is>
       </c>
@@ -4719,12 +4740,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>♣, −5</t>
+          <t>♣, −5, ratée</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>6 − 5</t>
+          <t>6 − 5 + 0</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -4759,12 +4780,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>♠</t>
+          <t>♠, ratée, ratée</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 + 0 + 0</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -4779,14 +4800,14 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>♥, −5
+          <t>♥, −5, ratée
 15, −5, −5
 ♣, ♠, −5</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>10 − 5
+          <t>10 − 5 + 0
 15 − 5 − 5
 6 + 4 − 5</t>
         </is>
@@ -4803,13 +4824,13 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>♣
+          <t>♣, ratée, ratée
 ♦, −5, −5</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>6
+          <t>6 + 0 + 0
 16 − 5 − 5</t>
         </is>
       </c>
@@ -4845,12 +4866,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>♠, ♠</t>
+          <t>♠, ♠, ratée</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>4 + 4</t>
+          <t>4 + 4 + 0</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -4885,16 +4906,16 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>♥
-15, −5
-♣, ♠</t>
+          <t>♥, ratée, ratée
+15, −5, ratée
+♣, ♠, ratée</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>10
-15 − 5
-6 + 4</t>
+          <t>10 + 0 + 0
+15 − 5 + 0
+6 + 4 + 0</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -4909,13 +4930,13 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>♦, −5
+          <t>♦, −5, ratée
 ♥, ♣, −5</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>16 − 5
+          <t>16 − 5 + 0
 10 + 6 − 5</t>
         </is>
       </c>
@@ -4931,12 +4952,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>♣, ♣</t>
+          <t>♣, ♣, ratée</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>6 + 6</t>
+          <t>6 + 6 + 0</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -4951,14 +4972,14 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>♥, ♠
+          <t>♥, ♠, ratée
 15, ♠, −5
 ♣, ♠, ♠</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>10 + 4
+          <t>10 + 4 + 0
 15 + 4 − 5
 6 + 4 + 4</t>
         </is>
@@ -4975,14 +4996,14 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>15
+          <t>15, ratée, ratée
 ♥, ♥, −5
 ♦, ♠, −5</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>15
+          <t>15 + 0 + 0
 10 + 10 − 5
 16 + 4 − 5</t>
         </is>
@@ -4999,16 +5020,16 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>♦
-♥, ♣
+          <t>♦, ratée, ratée
+♥, ♣, ratée
 15, ♣, −5
 ♣, ♣, ♠</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>16
-10 + 6
+          <t>16 + 0 + 0
+10 + 6 + 0
 15 + 6 − 5
 6 + 6 + 4</t>
         </is>
@@ -5065,12 +5086,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>15, ♠</t>
+          <t>15, ♠, ratée</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>15 + 4</t>
+          <t>15 + 4 + 0</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -5085,16 +5106,16 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>♥, ♥
-♦, ♠
+          <t>♥, ♥, ratée
+♦, ♠, ratée
 15, ♥, −5
 ♥, ♣, ♠</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>10 + 10
-16 + 4
+          <t>10 + 10 + 0
+16 + 4 + 0
 15 + 10 − 5
 10 + 6 + 4</t>
         </is>
@@ -5111,13 +5132,13 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>15, ♣
+          <t>15, ♣, ratée
 ♥, ♦, −5</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>15 + 6
+          <t>15 + 6 + 0
 10 + 16 − 5</t>
         </is>
       </c>
@@ -5133,13 +5154,13 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>♦, ♣
+          <t>♦, ♣, ratée
 ♥, ♣, ♣</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>16 + 6
+          <t>16 + 6 + 0
 10 + 6 + 6</t>
         </is>
       </c>
@@ -5197,13 +5218,13 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>15, ♥
+          <t>15, ♥, ratée
 15, ♣, ♠</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>15 + 10
+          <t>15 + 10 + 0
 15 + 6 + 4</t>
         </is>
       </c>
@@ -5219,7 +5240,7 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>♥, ♦
+          <t>♥, ♦, ratée
 15, ♦, −5
 ♥, ♥, ♣
 ♦, ♣, ♠</t>
@@ -5227,7 +5248,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>10 + 16
+          <t>10 + 16 + 0
 15 + 16 − 5
 10 + 10 + 6
 16 + 6 + 4</t>
@@ -5327,13 +5348,13 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>15, ♦
+          <t>15, ♦, ratée
 15, ♥, ♣</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>15 + 16
+          <t>15 + 16 + 0
 15 + 10 + 6</t>
         </is>
       </c>
@@ -5349,13 +5370,13 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>♦, ♦
+          <t>♦, ♦, ratée
 ♥, ♦, ♣</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>16 + 16
+          <t>16 + 16 + 0
 10 + 16 + 6</t>
         </is>
       </c>
@@ -5544,6 +5565,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Chaque ligne compte les 3 boules : 0, 1, 2 ou 3 boules peuvent rater (0 point chacune).</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5552,7 +5580,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Façons de l'obtenir (boules dans les trous ; les autres boules ratées = 0)</t>
+          <t>Façons de l'obtenir avec les 3 boules (ratée = boule dans aucun trou, 0 point)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -5572,12 +5600,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>−5, −5</t>
+          <t>−5, −5, ratée</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>−5 − 5</t>
+          <t>−5 − 5 + 0</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -5612,12 +5640,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>−5</t>
+          <t>−5, ratée, ratée</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>−5</t>
+          <t>−5 + 0 + 0</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -5672,12 +5700,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>♠, −5</t>
+          <t>♠, −5, ratée</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>4 − 5</t>
+          <t>4 − 5 + 0</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -5692,12 +5720,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>3 boules ratées</t>
+          <t>ratée, ratée, ratée</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0 + 0 + 0</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -5712,12 +5740,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>♣, −5</t>
+          <t>♣, −5, ratée</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>6 − 5</t>
+          <t>6 − 5 + 0</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -5732,13 +5760,13 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>♦, −5
+          <t>♦, −5, ratée
 ♠, ♠, −5</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>8 − 5
+          <t>8 − 5 + 0
 4 + 4 − 5</t>
         </is>
       </c>
@@ -5754,12 +5782,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>♠</t>
+          <t>♠, ratée, ratée</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 + 0 + 0</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -5796,12 +5824,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>♣</t>
+          <t>♣, ratée, ratée</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6 + 0 + 0</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -5838,14 +5866,14 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>♦
-♠, ♠</t>
+          <t>♦, ratée, ratée
+♠, ♠, ratée</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>8
-4 + 4</t>
+          <t>8 + 0 + 0
+4 + 4 + 0</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -5880,15 +5908,15 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>15, −5
-♣, ♠
+          <t>15, −5, ratée
+♣, ♠, ratée
 ♥, −5, −5</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>15 − 5
-6 + 4
+          <t>15 − 5 + 0
+6 + 4 + 0
 20 − 5 − 5</t>
         </is>
       </c>
@@ -5924,14 +5952,14 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>♦, ♠
-♣, ♣</t>
+          <t>♦, ♠, ratée
+♣, ♣, ratée</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>8 + 4
-6 + 6</t>
+          <t>8 + 4 + 0
+6 + 6 + 0</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -5946,14 +5974,14 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>♦, ♣
+          <t>♦, ♣, ratée
 15, ♠, −5
 ♣, ♠, ♠</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>8 + 6
+          <t>8 + 6 + 0
 15 + 4 − 5
 6 + 4 + 4</t>
         </is>
@@ -5970,14 +5998,14 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>15
-♥, −5</t>
+          <t>15, ratée, ratée
+♥, −5, ratée</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>15
-20 − 5</t>
+          <t>15 + 0 + 0
+20 − 5 + 0</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -5992,7 +6020,7 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>♦, ♦
+          <t>♦, ♦, ratée
 15, ♣, −5
 ♦, ♠, ♠
 ♣, ♣, ♠</t>
@@ -6000,7 +6028,7 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>8 + 8
+          <t>8 + 8 + 0
 15 + 6 − 5
 8 + 4 + 4
 6 + 6 + 4</t>
@@ -6040,13 +6068,13 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>15, ♠
+          <t>15, ♠, ratée
 ♥, ♠, −5</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>15 + 4
+          <t>15 + 4 + 0
 20 + 4 − 5</t>
         </is>
       </c>
@@ -6062,14 +6090,14 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>♥
+          <t>♥, ratée, ratée
 ♦, ♦, ♠
 ♦, ♣, ♣</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>20
+          <t>20 + 0 + 0
 8 + 8 + 4
 8 + 6 + 6</t>
         </is>
@@ -6086,13 +6114,13 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>15, ♣
+          <t>15, ♣, ratée
 ♥, ♣, −5</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>15 + 6
+          <t>15 + 6 + 0
 20 + 6 − 5</t>
         </is>
       </c>
@@ -6128,14 +6156,14 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>15, ♦
+          <t>15, ♦, ratée
 15, ♠, ♠
 ♥, ♦, −5</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>15 + 8
+          <t>15 + 8 + 0
 15 + 4 + 4
 20 + 8 − 5</t>
         </is>
@@ -6152,12 +6180,12 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>♥, ♠</t>
+          <t>♥, ♠, ratée</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>20 + 4</t>
+          <t>20 + 4 + 0</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -6192,12 +6220,12 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>♥, ♣</t>
+          <t>♥, ♣, ratée</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>20 + 6</t>
+          <t>20 + 6 + 0</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -6234,13 +6262,13 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>♥, ♦
+          <t>♥, ♦, ratée
 ♥, ♠, ♠</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>20 + 8
+          <t>20 + 8 + 0
 20 + 4 + 4</t>
         </is>
       </c>
@@ -6360,13 +6388,13 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>15, ♥
+          <t>15, ♥, ratée
 ♥, ♥, −5</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>15 + 20
+          <t>15 + 20 + 0
 20 + 20 − 5</t>
         </is>
       </c>
@@ -6422,12 +6450,12 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>♥, ♥</t>
+          <t>♥, ♥, ratée</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>20 + 20</t>
+          <t>20 + 20 + 0</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -6591,6 +6619,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Chaque ligne compte les 3 boules : 0, 1, 2 ou 3 boules peuvent rater (0 point chacune).</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -6599,7 +6634,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Façons de l'obtenir (boules dans les trous ; les autres boules ratées = 0)</t>
+          <t>Façons de l'obtenir avec les 3 boules (ratée = boule dans aucun trou, 0 point)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -6619,12 +6654,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>−5, −5</t>
+          <t>−5, −5, ratée</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>−10 − 10</t>
+          <t>−10 − 10 + 0</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -6659,12 +6694,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>−5</t>
+          <t>−5, ratée, ratée</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>−10</t>
+          <t>−10 + 0 + 0</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -6719,12 +6754,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>♠, −5</t>
+          <t>♠, −5, ratée</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>8 − 10</t>
+          <t>8 − 10 + 0</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -6739,13 +6774,13 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>3 boules ratées
+          <t>ratée, ratée, ratée
 ♥, −5, −5</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>0
+          <t>0 + 0 + 0
 20 − 10 − 10</t>
         </is>
       </c>
@@ -6761,12 +6796,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>♣, −5</t>
+          <t>♣, −5, ratée</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>12 − 10</t>
+          <t>12 − 10 + 0</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -6781,13 +6816,13 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>♦, −5
+          <t>♦, −5, ratée
 ♠, ♠, −5</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>16 − 10
+          <t>16 − 10 + 0
 8 + 8 − 10</t>
         </is>
       </c>
@@ -6803,12 +6838,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>♠</t>
+          <t>♠, ratée, ratée</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8 + 0 + 0</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -6823,14 +6858,14 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>♥, −5
+          <t>♥, −5, ratée
 15, −5, −5
 ♣, ♠, −5</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>20 − 10
+          <t>20 − 10 + 0
 30 − 10 − 10
 12 + 8 − 10</t>
         </is>
@@ -6847,12 +6882,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>♣</t>
+          <t>♣, ratée, ratée</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>12 + 0 + 0</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -6889,14 +6924,14 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>♦
-♠, ♠</t>
+          <t>♦, ratée, ratée
+♠, ♠, ratée</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>16
-8 + 8</t>
+          <t>16 + 0 + 0
+8 + 8 + 0</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -6933,16 +6968,16 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>♥
-15, −5
-♣, ♠</t>
+          <t>♥, ratée, ratée
+15, −5, ratée
+♣, ♠, ratée</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>20
-30 − 10
-12 + 8</t>
+          <t>20 + 0 + 0
+30 − 10 + 0
+12 + 8 + 0</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -6979,14 +7014,14 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>♦, ♠
-♣, ♣</t>
+          <t>♦, ♠, ratée
+♣, ♣, ratée</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>16 + 8
-12 + 12</t>
+          <t>16 + 8 + 0
+12 + 12 + 0</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -7021,16 +7056,16 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>♥, ♠
-♦, ♣
+          <t>♥, ♠, ratée
+♦, ♣, ratée
 15, ♠, −5
 ♣, ♠, ♠</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>20 + 8
-16 + 12
+          <t>20 + 8 + 0
+16 + 12 + 0
 30 + 8 − 10
 12 + 8 + 8</t>
         </is>
@@ -7047,13 +7082,13 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>15
+          <t>15, ratée, ratée
 ♥, ♥, −5</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>30
+          <t>30 + 0 + 0
 20 + 20 − 10</t>
         </is>
       </c>
@@ -7069,8 +7104,8 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>♥, ♣
-♦, ♦
+          <t>♥, ♣, ratée
+♦, ♦, ratée
 15, ♣, −5
 ♦, ♠, ♠
 ♣, ♣, ♠</t>
@@ -7078,8 +7113,8 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>20 + 12
-16 + 16
+          <t>20 + 12 + 0
+16 + 16 + 0
 30 + 12 − 10
 16 + 8 + 8
 12 + 12 + 8</t>
@@ -7097,7 +7132,7 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>♥, ♦
+          <t>♥, ♦, ratée
 15, ♦, −5
 ♥, ♠, ♠
 ♦, ♣, ♠</t>
@@ -7105,7 +7140,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>20 + 16
+          <t>20 + 16 + 0
 30 + 16 − 10
 20 + 8 + 8
 16 + 12 + 8</t>
@@ -7123,12 +7158,12 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>15, ♠</t>
+          <t>15, ♠, ratée</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>30 + 8</t>
+          <t>30 + 8 + 0</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -7143,7 +7178,7 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>♥, ♥
+          <t>♥, ♥, ratée
 15, ♥, −5
 ♥, ♣, ♠
 ♦, ♦, ♠
@@ -7152,7 +7187,7 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>20 + 20
+          <t>20 + 20 + 0
 30 + 20 − 10
 20 + 12 + 8
 16 + 16 + 8
@@ -7171,12 +7206,12 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>15, ♣</t>
+          <t>15, ♣, ratée</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>30 + 12</t>
+          <t>30 + 12 + 0</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -7215,13 +7250,13 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>15, ♦
+          <t>15, ♦, ratée
 15, ♠, ♠</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>30 + 16
+          <t>30 + 16 + 0
 30 + 8 + 8</t>
         </is>
       </c>
@@ -7259,13 +7294,13 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>15, ♥
+          <t>15, ♥, ratée
 15, ♣, ♠</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>30 + 20
+          <t>30 + 20 + 0
 30 + 12 + 8</t>
         </is>
       </c>
